--- a/artfynd/A 47475-2024 artfynd.xlsx
+++ b/artfynd/A 47475-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1005,6 +1005,312 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122239487</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78917</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1816</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Luddig stiftdynlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Micarea hedlundii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Coppins</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skeppsberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>577422</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6653090</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122239488</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98149</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skeppsberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>577375</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6653094</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122239486</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98149</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skeppsberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>577462</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6653099</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47475-2024 artfynd.xlsx
+++ b/artfynd/A 47475-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1312,6 +1312,238 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122261333</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98157</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skeppsberget, 700 m OSO om (knärot), Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>577462</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6653098</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>U-Sal-1134</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122261284</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98157</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skeppsberget, 600 m OSO om (knärot), Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>577375</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6653095</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>U-Sal-1133</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47475-2024 artfynd.xlsx
+++ b/artfynd/A 47475-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122239487</v>
+        <v>122239488</v>
       </c>
       <c r="B5" t="n">
-        <v>78917</v>
+        <v>98157</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1816</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddig stiftdynlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Micarea hedlundii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Coppins</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577422</v>
+        <v>577375</v>
       </c>
       <c r="R5" t="n">
-        <v>6653090</v>
+        <v>6653094</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122239488</v>
+        <v>122239487</v>
       </c>
       <c r="B6" t="n">
-        <v>98149</v>
+        <v>78921</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,21 +1126,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1816</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddig stiftdynlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Micarea hedlundii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Coppins</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577375</v>
+        <v>577422</v>
       </c>
       <c r="R6" t="n">
-        <v>6653094</v>
+        <v>6653090</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1215,7 +1215,7 @@
         <v>122239486</v>
       </c>
       <c r="B7" t="n">
-        <v>98149</v>
+        <v>98157</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 47475-2024 artfynd.xlsx
+++ b/artfynd/A 47475-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122239488</v>
+        <v>122239486</v>
       </c>
       <c r="B5" t="n">
-        <v>98157</v>
+        <v>98159</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577375</v>
+        <v>577462</v>
       </c>
       <c r="R5" t="n">
-        <v>6653094</v>
+        <v>6653099</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122239487</v>
+        <v>122239488</v>
       </c>
       <c r="B6" t="n">
-        <v>78921</v>
+        <v>98159</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,21 +1126,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1816</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddig stiftdynlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Micarea hedlundii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Coppins</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577422</v>
+        <v>577375</v>
       </c>
       <c r="R6" t="n">
-        <v>6653090</v>
+        <v>6653094</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122239486</v>
+        <v>122239487</v>
       </c>
       <c r="B7" t="n">
-        <v>98157</v>
+        <v>78923</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1228,21 +1228,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1816</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddig stiftdynlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Micarea hedlundii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Coppins</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577462</v>
+        <v>577422</v>
       </c>
       <c r="R7" t="n">
-        <v>6653099</v>
+        <v>6653090</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1317,7 +1317,7 @@
         <v>122261333</v>
       </c>
       <c r="B8" t="n">
-        <v>98157</v>
+        <v>98159</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>122261284</v>
       </c>
       <c r="B9" t="n">
-        <v>98157</v>
+        <v>98159</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 47475-2024 artfynd.xlsx
+++ b/artfynd/A 47475-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122239486</v>
+        <v>122239487</v>
       </c>
       <c r="B5" t="n">
-        <v>98159</v>
+        <v>78923</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1816</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddig stiftdynlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Micarea hedlundii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Coppins</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577462</v>
+        <v>577422</v>
       </c>
       <c r="R5" t="n">
-        <v>6653099</v>
+        <v>6653090</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1110,7 +1110,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122239488</v>
+        <v>122239486</v>
       </c>
       <c r="B6" t="n">
         <v>98159</v>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577375</v>
+        <v>577462</v>
       </c>
       <c r="R6" t="n">
-        <v>6653094</v>
+        <v>6653099</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122239487</v>
+        <v>122239488</v>
       </c>
       <c r="B7" t="n">
-        <v>78923</v>
+        <v>98159</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1228,21 +1228,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1816</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddig stiftdynlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Micarea hedlundii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Coppins</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577422</v>
+        <v>577375</v>
       </c>
       <c r="R7" t="n">
-        <v>6653090</v>
+        <v>6653094</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1314,7 +1314,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122261333</v>
+        <v>122261284</v>
       </c>
       <c r="B8" t="n">
         <v>98159</v>
@@ -1354,14 +1354,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skeppsberget, 700 m OSO om (knärot), Vstm</t>
+          <t>Skeppsberget, 600 m OSO om (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577462</v>
+        <v>577375</v>
       </c>
       <c r="R8" t="n">
-        <v>6653098</v>
+        <v>6653095</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>U-Sal-1134</t>
+          <t>U-Sal-1133</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1430,7 +1430,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122261284</v>
+        <v>122261333</v>
       </c>
       <c r="B9" t="n">
         <v>98159</v>
@@ -1470,14 +1470,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skeppsberget, 600 m OSO om (knärot), Vstm</t>
+          <t>Skeppsberget, 700 m OSO om (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577375</v>
+        <v>577462</v>
       </c>
       <c r="R9" t="n">
-        <v>6653095</v>
+        <v>6653098</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>U-Sal-1133</t>
+          <t>U-Sal-1134</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">

--- a/artfynd/A 47475-2024 artfynd.xlsx
+++ b/artfynd/A 47475-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122239487</v>
+        <v>122239488</v>
       </c>
       <c r="B5" t="n">
-        <v>78923</v>
+        <v>98175</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1816</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddig stiftdynlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Micarea hedlundii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Coppins</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577422</v>
+        <v>577375</v>
       </c>
       <c r="R5" t="n">
-        <v>6653090</v>
+        <v>6653094</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122239486</v>
+        <v>122239487</v>
       </c>
       <c r="B6" t="n">
-        <v>98159</v>
+        <v>78923</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,21 +1126,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1816</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddig stiftdynlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Micarea hedlundii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Coppins</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577462</v>
+        <v>577422</v>
       </c>
       <c r="R6" t="n">
-        <v>6653099</v>
+        <v>6653090</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122239488</v>
+        <v>122239486</v>
       </c>
       <c r="B7" t="n">
-        <v>98159</v>
+        <v>98175</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577375</v>
+        <v>577462</v>
       </c>
       <c r="R7" t="n">
-        <v>6653094</v>
+        <v>6653099</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1314,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122261284</v>
+        <v>122261333</v>
       </c>
       <c r="B8" t="n">
-        <v>98159</v>
+        <v>98175</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1354,14 +1354,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skeppsberget, 600 m OSO om (knärot), Vstm</t>
+          <t>Skeppsberget, 700 m OSO om (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577375</v>
+        <v>577462</v>
       </c>
       <c r="R8" t="n">
-        <v>6653095</v>
+        <v>6653098</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>U-Sal-1133</t>
+          <t>U-Sal-1134</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1430,10 +1430,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122261333</v>
+        <v>122261284</v>
       </c>
       <c r="B9" t="n">
-        <v>98159</v>
+        <v>98175</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,14 +1470,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skeppsberget, 700 m OSO om (knärot), Vstm</t>
+          <t>Skeppsberget, 600 m OSO om (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577462</v>
+        <v>577375</v>
       </c>
       <c r="R9" t="n">
-        <v>6653098</v>
+        <v>6653095</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>U-Sal-1134</t>
+          <t>U-Sal-1133</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">

--- a/artfynd/A 47475-2024 artfynd.xlsx
+++ b/artfynd/A 47475-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122239488</v>
+        <v>122239487</v>
       </c>
       <c r="B5" t="n">
-        <v>98175</v>
+        <v>78923</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1816</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddig stiftdynlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Micarea hedlundii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Coppins</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577375</v>
+        <v>577422</v>
       </c>
       <c r="R5" t="n">
-        <v>6653094</v>
+        <v>6653090</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122239487</v>
+        <v>122239486</v>
       </c>
       <c r="B6" t="n">
-        <v>78923</v>
+        <v>98175</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,21 +1126,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1816</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddig stiftdynlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Micarea hedlundii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Coppins</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577422</v>
+        <v>577462</v>
       </c>
       <c r="R6" t="n">
-        <v>6653090</v>
+        <v>6653099</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,7 +1212,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122239486</v>
+        <v>122239488</v>
       </c>
       <c r="B7" t="n">
         <v>98175</v>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577462</v>
+        <v>577375</v>
       </c>
       <c r="R7" t="n">
-        <v>6653099</v>
+        <v>6653094</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1314,7 +1314,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122261333</v>
+        <v>122261284</v>
       </c>
       <c r="B8" t="n">
         <v>98175</v>
@@ -1354,14 +1354,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skeppsberget, 700 m OSO om (knärot), Vstm</t>
+          <t>Skeppsberget, 600 m OSO om (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577462</v>
+        <v>577375</v>
       </c>
       <c r="R8" t="n">
-        <v>6653098</v>
+        <v>6653095</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>U-Sal-1134</t>
+          <t>U-Sal-1133</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1430,7 +1430,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122261284</v>
+        <v>122261333</v>
       </c>
       <c r="B9" t="n">
         <v>98175</v>
@@ -1470,14 +1470,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skeppsberget, 600 m OSO om (knärot), Vstm</t>
+          <t>Skeppsberget, 700 m OSO om (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577375</v>
+        <v>577462</v>
       </c>
       <c r="R9" t="n">
-        <v>6653095</v>
+        <v>6653098</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>U-Sal-1133</t>
+          <t>U-Sal-1134</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">

--- a/artfynd/A 47475-2024 artfynd.xlsx
+++ b/artfynd/A 47475-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122239487</v>
+        <v>122239486</v>
       </c>
       <c r="B5" t="n">
-        <v>78923</v>
+        <v>98185</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1816</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddig stiftdynlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Micarea hedlundii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Coppins</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577422</v>
+        <v>577462</v>
       </c>
       <c r="R5" t="n">
-        <v>6653090</v>
+        <v>6653099</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122239486</v>
+        <v>122239488</v>
       </c>
       <c r="B6" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577462</v>
+        <v>577375</v>
       </c>
       <c r="R6" t="n">
-        <v>6653099</v>
+        <v>6653094</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122239488</v>
+        <v>122239487</v>
       </c>
       <c r="B7" t="n">
-        <v>98175</v>
+        <v>78924</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1228,21 +1228,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1816</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddig stiftdynlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Micarea hedlundii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Coppins</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577375</v>
+        <v>577422</v>
       </c>
       <c r="R7" t="n">
-        <v>6653094</v>
+        <v>6653090</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1314,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122261284</v>
+        <v>122261333</v>
       </c>
       <c r="B8" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1354,14 +1354,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skeppsberget, 600 m OSO om (knärot), Vstm</t>
+          <t>Skeppsberget, 700 m OSO om (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577375</v>
+        <v>577462</v>
       </c>
       <c r="R8" t="n">
-        <v>6653095</v>
+        <v>6653098</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>U-Sal-1133</t>
+          <t>U-Sal-1134</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1430,10 +1430,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122261333</v>
+        <v>122261284</v>
       </c>
       <c r="B9" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,14 +1470,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skeppsberget, 700 m OSO om (knärot), Vstm</t>
+          <t>Skeppsberget, 600 m OSO om (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577462</v>
+        <v>577375</v>
       </c>
       <c r="R9" t="n">
-        <v>6653098</v>
+        <v>6653095</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>U-Sal-1134</t>
+          <t>U-Sal-1133</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">

--- a/artfynd/A 47475-2024 artfynd.xlsx
+++ b/artfynd/A 47475-2024 artfynd.xlsx
@@ -1110,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122239488</v>
+        <v>122239487</v>
       </c>
       <c r="B6" t="n">
-        <v>98185</v>
+        <v>78924</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,21 +1126,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1816</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddig stiftdynlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Micarea hedlundii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Coppins</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577375</v>
+        <v>577422</v>
       </c>
       <c r="R6" t="n">
-        <v>6653094</v>
+        <v>6653090</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122239487</v>
+        <v>122239488</v>
       </c>
       <c r="B7" t="n">
-        <v>78924</v>
+        <v>98185</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1228,21 +1228,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1816</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddig stiftdynlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Micarea hedlundii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Coppins</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577422</v>
+        <v>577375</v>
       </c>
       <c r="R7" t="n">
-        <v>6653090</v>
+        <v>6653094</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1314,7 +1314,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122261333</v>
+        <v>122261284</v>
       </c>
       <c r="B8" t="n">
         <v>98185</v>
@@ -1354,14 +1354,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skeppsberget, 700 m OSO om (knärot), Vstm</t>
+          <t>Skeppsberget, 600 m OSO om (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577462</v>
+        <v>577375</v>
       </c>
       <c r="R8" t="n">
-        <v>6653098</v>
+        <v>6653095</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>U-Sal-1134</t>
+          <t>U-Sal-1133</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1430,7 +1430,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122261284</v>
+        <v>122261333</v>
       </c>
       <c r="B9" t="n">
         <v>98185</v>
@@ -1470,14 +1470,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skeppsberget, 600 m OSO om (knärot), Vstm</t>
+          <t>Skeppsberget, 700 m OSO om (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577375</v>
+        <v>577462</v>
       </c>
       <c r="R9" t="n">
-        <v>6653095</v>
+        <v>6653098</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>U-Sal-1133</t>
+          <t>U-Sal-1134</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">

--- a/artfynd/A 47475-2024 artfynd.xlsx
+++ b/artfynd/A 47475-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122239486</v>
+        <v>122239487</v>
       </c>
       <c r="B5" t="n">
-        <v>98185</v>
+        <v>78929</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1816</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddig stiftdynlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Micarea hedlundii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Coppins</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577462</v>
+        <v>577422</v>
       </c>
       <c r="R5" t="n">
-        <v>6653099</v>
+        <v>6653090</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122239487</v>
+        <v>122239488</v>
       </c>
       <c r="B6" t="n">
-        <v>78924</v>
+        <v>98197</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,21 +1126,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1816</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddig stiftdynlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Micarea hedlundii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Coppins</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577422</v>
+        <v>577375</v>
       </c>
       <c r="R6" t="n">
-        <v>6653090</v>
+        <v>6653094</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122239488</v>
+        <v>122239486</v>
       </c>
       <c r="B7" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577375</v>
+        <v>577462</v>
       </c>
       <c r="R7" t="n">
-        <v>6653094</v>
+        <v>6653099</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1317,7 +1317,7 @@
         <v>122261284</v>
       </c>
       <c r="B8" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>122261333</v>
       </c>
       <c r="B9" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 47475-2024 artfynd.xlsx
+++ b/artfynd/A 47475-2024 artfynd.xlsx
@@ -1110,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122239488</v>
+        <v>122239486</v>
       </c>
       <c r="B6" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577375</v>
+        <v>577462</v>
       </c>
       <c r="R6" t="n">
-        <v>6653094</v>
+        <v>6653099</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122239486</v>
+        <v>122239488</v>
       </c>
       <c r="B7" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577462</v>
+        <v>577375</v>
       </c>
       <c r="R7" t="n">
-        <v>6653099</v>
+        <v>6653094</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1314,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122261284</v>
+        <v>122261333</v>
       </c>
       <c r="B8" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1354,14 +1354,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skeppsberget, 600 m OSO om (knärot), Vstm</t>
+          <t>Skeppsberget, 700 m OSO om (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577375</v>
+        <v>577462</v>
       </c>
       <c r="R8" t="n">
-        <v>6653095</v>
+        <v>6653098</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>U-Sal-1133</t>
+          <t>U-Sal-1134</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1430,10 +1430,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122261333</v>
+        <v>122261284</v>
       </c>
       <c r="B9" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,14 +1470,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skeppsberget, 700 m OSO om (knärot), Vstm</t>
+          <t>Skeppsberget, 600 m OSO om (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577462</v>
+        <v>577375</v>
       </c>
       <c r="R9" t="n">
-        <v>6653098</v>
+        <v>6653095</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>U-Sal-1134</t>
+          <t>U-Sal-1133</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">

--- a/artfynd/A 47475-2024 artfynd.xlsx
+++ b/artfynd/A 47475-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122239487</v>
+        <v>122239486</v>
       </c>
       <c r="B5" t="n">
-        <v>78929</v>
+        <v>98211</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1816</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Luddig stiftdynlav</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Micarea hedlundii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Coppins</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577422</v>
+        <v>577462</v>
       </c>
       <c r="R5" t="n">
-        <v>6653090</v>
+        <v>6653099</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1110,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122239486</v>
+        <v>122239487</v>
       </c>
       <c r="B6" t="n">
-        <v>98202</v>
+        <v>78930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,21 +1121,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>1816</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Micarea hedlundii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Coppins</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577462</v>
+        <v>577422</v>
       </c>
       <c r="R6" t="n">
-        <v>6653099</v>
+        <v>6653090</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1215,7 +1205,7 @@
         <v>122239488</v>
       </c>
       <c r="B7" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,11 +1219,6 @@
       </c>
       <c r="E7" t="n">
         <v>220787</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1314,10 +1299,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122261333</v>
+        <v>122261284</v>
       </c>
       <c r="B8" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,11 +1316,6 @@
       </c>
       <c r="E8" t="n">
         <v>220787</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1354,14 +1334,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skeppsberget, 700 m OSO om (knärot), Vstm</t>
+          <t>Skeppsberget, 600 m OSO om (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577462</v>
+        <v>577375</v>
       </c>
       <c r="R8" t="n">
-        <v>6653098</v>
+        <v>6653095</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1388,7 +1368,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>U-Sal-1134</t>
+          <t>U-Sal-1133</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1430,10 +1410,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122261284</v>
+        <v>122261333</v>
       </c>
       <c r="B9" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,11 +1427,6 @@
       </c>
       <c r="E9" t="n">
         <v>220787</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1470,14 +1445,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skeppsberget, 600 m OSO om (knärot), Vstm</t>
+          <t>Skeppsberget, 700 m OSO om (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577375</v>
+        <v>577462</v>
       </c>
       <c r="R9" t="n">
-        <v>6653095</v>
+        <v>6653098</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1504,7 +1479,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>U-Sal-1133</t>
+          <t>U-Sal-1134</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">

--- a/artfynd/A 47475-2024 artfynd.xlsx
+++ b/artfynd/A 47475-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122239486</v>
+        <v>122239487</v>
       </c>
       <c r="B5" t="n">
-        <v>98211</v>
+        <v>78934</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,16 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1816</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Luddig stiftdynlav</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Micarea hedlundii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Coppins</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577462</v>
+        <v>577422</v>
       </c>
       <c r="R5" t="n">
-        <v>6653099</v>
+        <v>6653090</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1105,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122239487</v>
+        <v>122239486</v>
       </c>
       <c r="B6" t="n">
-        <v>78930</v>
+        <v>98224</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,16 +1126,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1816</v>
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Micarea hedlundii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Coppins</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1140,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577422</v>
+        <v>577462</v>
       </c>
       <c r="R6" t="n">
-        <v>6653090</v>
+        <v>6653099</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1205,7 +1215,7 @@
         <v>122239488</v>
       </c>
       <c r="B7" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,6 +1229,11 @@
       </c>
       <c r="E7" t="n">
         <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1302,7 +1317,7 @@
         <v>122261284</v>
       </c>
       <c r="B8" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1316,6 +1331,11 @@
       </c>
       <c r="E8" t="n">
         <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1413,7 +1433,7 @@
         <v>122261333</v>
       </c>
       <c r="B9" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1427,6 +1447,11 @@
       </c>
       <c r="E9" t="n">
         <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>

--- a/artfynd/A 47475-2024 artfynd.xlsx
+++ b/artfynd/A 47475-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122239487</v>
+        <v>122239488</v>
       </c>
       <c r="B5" t="n">
-        <v>78934</v>
+        <v>98237</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1816</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddig stiftdynlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Micarea hedlundii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Coppins</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577422</v>
+        <v>577375</v>
       </c>
       <c r="R5" t="n">
-        <v>6653090</v>
+        <v>6653094</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122239486</v>
+        <v>122239487</v>
       </c>
       <c r="B6" t="n">
-        <v>98224</v>
+        <v>78934</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,21 +1126,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1816</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddig stiftdynlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Micarea hedlundii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Coppins</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577462</v>
+        <v>577422</v>
       </c>
       <c r="R6" t="n">
-        <v>6653099</v>
+        <v>6653090</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122239488</v>
+        <v>122239486</v>
       </c>
       <c r="B7" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577375</v>
+        <v>577462</v>
       </c>
       <c r="R7" t="n">
-        <v>6653094</v>
+        <v>6653099</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1314,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122261284</v>
+        <v>122261333</v>
       </c>
       <c r="B8" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1354,14 +1354,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skeppsberget, 600 m OSO om (knärot), Vstm</t>
+          <t>Skeppsberget, 700 m OSO om (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577375</v>
+        <v>577462</v>
       </c>
       <c r="R8" t="n">
-        <v>6653095</v>
+        <v>6653098</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>U-Sal-1133</t>
+          <t>U-Sal-1134</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1430,10 +1430,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122261333</v>
+        <v>122261284</v>
       </c>
       <c r="B9" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,14 +1470,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skeppsberget, 700 m OSO om (knärot), Vstm</t>
+          <t>Skeppsberget, 600 m OSO om (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577462</v>
+        <v>577375</v>
       </c>
       <c r="R9" t="n">
-        <v>6653098</v>
+        <v>6653095</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>U-Sal-1134</t>
+          <t>U-Sal-1133</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">

--- a/artfynd/A 47475-2024 artfynd.xlsx
+++ b/artfynd/A 47475-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122239488</v>
+        <v>122239487</v>
       </c>
       <c r="B5" t="n">
-        <v>98237</v>
+        <v>78934</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1816</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddig stiftdynlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Micarea hedlundii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Coppins</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577375</v>
+        <v>577422</v>
       </c>
       <c r="R5" t="n">
-        <v>6653094</v>
+        <v>6653090</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122239487</v>
+        <v>122239488</v>
       </c>
       <c r="B6" t="n">
-        <v>78934</v>
+        <v>98237</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,21 +1126,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1816</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddig stiftdynlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Micarea hedlundii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Coppins</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577422</v>
+        <v>577375</v>
       </c>
       <c r="R6" t="n">
-        <v>6653090</v>
+        <v>6653094</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 47475-2024 artfynd.xlsx
+++ b/artfynd/A 47475-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122239487</v>
+        <v>122239488</v>
       </c>
       <c r="B5" t="n">
-        <v>78934</v>
+        <v>98240</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1816</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddig stiftdynlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Micarea hedlundii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Coppins</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577422</v>
+        <v>577375</v>
       </c>
       <c r="R5" t="n">
-        <v>6653090</v>
+        <v>6653094</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122239488</v>
+        <v>122239486</v>
       </c>
       <c r="B6" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577375</v>
+        <v>577462</v>
       </c>
       <c r="R6" t="n">
-        <v>6653094</v>
+        <v>6653099</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122239486</v>
+        <v>122239487</v>
       </c>
       <c r="B7" t="n">
-        <v>98237</v>
+        <v>78934</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1228,21 +1228,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1816</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddig stiftdynlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Micarea hedlundii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Coppins</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577462</v>
+        <v>577422</v>
       </c>
       <c r="R7" t="n">
-        <v>6653099</v>
+        <v>6653090</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1314,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122261333</v>
+        <v>122261284</v>
       </c>
       <c r="B8" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1354,14 +1354,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skeppsberget, 700 m OSO om (knärot), Vstm</t>
+          <t>Skeppsberget, 600 m OSO om (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577462</v>
+        <v>577375</v>
       </c>
       <c r="R8" t="n">
-        <v>6653098</v>
+        <v>6653095</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>U-Sal-1134</t>
+          <t>U-Sal-1133</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1430,10 +1430,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122261284</v>
+        <v>122261333</v>
       </c>
       <c r="B9" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,14 +1470,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skeppsberget, 600 m OSO om (knärot), Vstm</t>
+          <t>Skeppsberget, 700 m OSO om (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577375</v>
+        <v>577462</v>
       </c>
       <c r="R9" t="n">
-        <v>6653095</v>
+        <v>6653098</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>U-Sal-1133</t>
+          <t>U-Sal-1134</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">

--- a/artfynd/A 47475-2024 artfynd.xlsx
+++ b/artfynd/A 47475-2024 artfynd.xlsx
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122239488</v>
+        <v>122239486</v>
       </c>
       <c r="B5" t="n">
         <v>98240</v>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577375</v>
+        <v>577462</v>
       </c>
       <c r="R5" t="n">
-        <v>6653094</v>
+        <v>6653099</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122239486</v>
+        <v>122239487</v>
       </c>
       <c r="B6" t="n">
-        <v>98240</v>
+        <v>78934</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,21 +1126,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1816</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddig stiftdynlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Micarea hedlundii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Coppins</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577462</v>
+        <v>577422</v>
       </c>
       <c r="R6" t="n">
-        <v>6653099</v>
+        <v>6653090</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122239487</v>
+        <v>122239488</v>
       </c>
       <c r="B7" t="n">
-        <v>78934</v>
+        <v>98240</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1228,21 +1228,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1816</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddig stiftdynlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Micarea hedlundii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Coppins</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577422</v>
+        <v>577375</v>
       </c>
       <c r="R7" t="n">
-        <v>6653090</v>
+        <v>6653094</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>

--- a/artfynd/A 47475-2024 artfynd.xlsx
+++ b/artfynd/A 47475-2024 artfynd.xlsx
@@ -1317,7 +1317,7 @@
         <v>122261284</v>
       </c>
       <c r="B8" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>122261333</v>
       </c>
       <c r="B9" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 47475-2024 artfynd.xlsx
+++ b/artfynd/A 47475-2024 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>113273328</v>
       </c>
       <c r="B4" t="n">
-        <v>97650</v>
+        <v>98357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,7 +930,19 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Myggsjön, Vstm</t>
@@ -981,6 +993,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47475-2024 artfynd.xlsx
+++ b/artfynd/A 47475-2024 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>113273328</v>
       </c>
       <c r="B4" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 47475-2024 artfynd.xlsx
+++ b/artfynd/A 47475-2024 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>113273328</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 47475-2024 artfynd.xlsx
+++ b/artfynd/A 47475-2024 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>113273328</v>
       </c>
       <c r="B4" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 47475-2024 artfynd.xlsx
+++ b/artfynd/A 47475-2024 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>113273328</v>
       </c>
       <c r="B4" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 47475-2024 artfynd.xlsx
+++ b/artfynd/A 47475-2024 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>113273328</v>
       </c>
       <c r="B4" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 47475-2024 artfynd.xlsx
+++ b/artfynd/A 47475-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113273323</v>
+        <v>113273292</v>
       </c>
       <c r="B2" t="n">
-        <v>78780</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1816</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddig stiftdynlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Micarea hedlundii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Coppins</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577442</v>
+        <v>577528</v>
       </c>
       <c r="R2" t="n">
-        <v>6653092</v>
+        <v>6653083</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,7 +759,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>tallåga fuktig</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -789,16 +784,11 @@
         <v>113273315</v>
       </c>
       <c r="B3" t="n">
-        <v>90774</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -811,12 +801,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -897,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113273328</v>
+        <v>113273323</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79606</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,46 +898,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1816</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddig stiftdynlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Micarea hedlundii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>Coppins</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Myggsjön, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577402</v>
+        <v>577442</v>
       </c>
       <c r="R4" t="n">
-        <v>6653099</v>
+        <v>6653092</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,13 +966,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>tallåga fuktig</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1021,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122239486</v>
+        <v>122239487</v>
       </c>
       <c r="B5" t="n">
-        <v>98240</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79606</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1816</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddig stiftdynlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Micarea hedlundii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Coppins</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577462</v>
+        <v>577422</v>
       </c>
       <c r="R5" t="n">
-        <v>6653099</v>
+        <v>6653090</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1123,37 +1090,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122239487</v>
+        <v>122239471</v>
       </c>
       <c r="B6" t="n">
-        <v>78934</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1816</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddig stiftdynlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Micarea hedlundii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Coppins</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1125,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577422</v>
+        <v>577481</v>
       </c>
       <c r="R6" t="n">
-        <v>6653090</v>
+        <v>6653050</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1225,15 +1187,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122239488</v>
+        <v>113273328</v>
       </c>
       <c r="B7" t="n">
-        <v>98240</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,17 +1215,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skeppsberget, Vstm</t>
+          <t>Myggsjön, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577375</v>
+        <v>577402</v>
       </c>
       <c r="R7" t="n">
-        <v>6653094</v>
+        <v>6653099</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1295,12 +1264,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1309,8 +1278,14 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1323,19 +1298,18 @@
           <t>Mikael Hagström</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122261284</v>
+        <v>122239486</v>
       </c>
       <c r="B8" t="n">
-        <v>98241</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,20 +1335,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skeppsberget, 600 m OSO om (knärot), Vstm</t>
+          <t>Skeppsberget, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577375</v>
+        <v>577462</v>
       </c>
       <c r="R8" t="n">
-        <v>6653095</v>
+        <v>6653098</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1399,11 +1369,6 @@
           <t>Västerfärnebo</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>U-Sal-1133</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
           <t>2024-08-30</t>
@@ -1420,14 +1385,13 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -1435,23 +1399,14 @@
           <t>Mikael Hagström</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122261333</v>
+        <v>122239488</v>
       </c>
       <c r="B9" t="n">
-        <v>98241</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1477,20 +1432,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skeppsberget, 700 m OSO om (knärot), Vstm</t>
+          <t>Skeppsberget, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577462</v>
+        <v>577375</v>
       </c>
       <c r="R9" t="n">
-        <v>6653098</v>
+        <v>6653094</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1515,11 +1466,6 @@
           <t>Västerfärnebo</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>U-Sal-1134</t>
-        </is>
-      </c>
       <c r="Y9" t="inlineStr">
         <is>
           <t>2024-08-30</t>
@@ -1536,24 +1482,328 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122261284</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skeppsberget, 600 m OSO om (knärot), Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>577375</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6653095</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>U-Sal-1133</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Bo Eriksson</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>113273317</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Myggsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>577436</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6653053</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-07-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-07-13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>113273334</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Myggsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>577492</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6653051</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-07-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-07-13</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 47475-2024 artfynd.xlsx
+++ b/artfynd/A 47475-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113273292</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113273315</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113273323</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122239487</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122239471</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1303,6 +1333,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113273328</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1400,6 +1435,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122239486</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1497,6 +1537,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122239488</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1608,6 +1653,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122261284</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1709,6 +1759,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113273317</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1806,8 +1861,26 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113273334</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>